--- a/feedback_surveys/022_remediation_services_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/022_remediation_services_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'option1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'option2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'option3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option4',_'value':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'option4', 'value': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option5',_'value':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'option5', 'value': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option6',_'value':_'option6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'option6', 'value': 'option6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option7',_'value':_'option7'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'option7', 'value': 'option7'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option8',_'value':_'option8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'option8', 'value': 'option8'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option9',_'value':_'option9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'option9', 'value': 'option9'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option10',_'value':_'option10'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'option10', 'value': 'option10'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option11',_'value':_'option11'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'option11', 'value': 'option11'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option12',_'value':_'option12'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'option12', 'value': 'option12'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option13',_'value':_'option13'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'option13', 'value': 'option13'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option14',_'value':_'option14'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'option14', 'value': 'option14'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'option15',_'value':_'option15'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'option15', 'value': 'option15'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option16',_'value':_'option16'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'option16', 'value': 'option16'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'option17',_'value':_'option17'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'option17', 'value': 'option17'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'option18',_'value':_'option18'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'option18', 'value': 'option18'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
